--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TracerProjects2\WNBA_Elo\Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC7BD83-3F53-4E86-8B4E-C197CBCFF7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1742D1D-7C1B-441B-B2D9-3B04FDF512BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -14156,6 +14156,15 @@
       <c r="G426" t="s">
         <v>24</v>
       </c>
+      <c r="H426">
+        <v>89</v>
+      </c>
+      <c r="I426">
+        <v>98</v>
+      </c>
+      <c r="J426">
+        <v>0</v>
+      </c>
     </row>
     <row r="427" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A427" s="1">
@@ -14179,6 +14188,15 @@
       <c r="G427" t="s">
         <v>25</v>
       </c>
+      <c r="H427">
+        <v>98</v>
+      </c>
+      <c r="I427">
+        <v>89</v>
+      </c>
+      <c r="J427">
+        <v>0</v>
+      </c>
     </row>
     <row r="428" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A428" s="1">
@@ -14202,6 +14220,15 @@
       <c r="G428" t="s">
         <v>24</v>
       </c>
+      <c r="H428">
+        <v>112</v>
+      </c>
+      <c r="I428">
+        <v>98</v>
+      </c>
+      <c r="J428">
+        <v>0</v>
+      </c>
     </row>
     <row r="429" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A429" s="1">
@@ -14225,6 +14252,15 @@
       <c r="G429" t="s">
         <v>25</v>
       </c>
+      <c r="H429">
+        <v>98</v>
+      </c>
+      <c r="I429">
+        <v>112</v>
+      </c>
+      <c r="J429">
+        <v>0</v>
+      </c>
     </row>
     <row r="430" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A430" s="1">
@@ -14248,6 +14284,15 @@
       <c r="G430" t="s">
         <v>24</v>
       </c>
+      <c r="H430">
+        <v>75</v>
+      </c>
+      <c r="I430">
+        <v>81</v>
+      </c>
+      <c r="J430">
+        <v>0</v>
+      </c>
     </row>
     <row r="431" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A431" s="1">
@@ -14271,6 +14316,15 @@
       <c r="G431" t="s">
         <v>25</v>
       </c>
+      <c r="H431">
+        <v>81</v>
+      </c>
+      <c r="I431">
+        <v>75</v>
+      </c>
+      <c r="J431">
+        <v>0</v>
+      </c>
     </row>
     <row r="432" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A432" s="1">
@@ -14294,8 +14348,17 @@
       <c r="G432" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H432">
+        <v>83</v>
+      </c>
+      <c r="I432">
+        <v>84</v>
+      </c>
+      <c r="J432">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A433" s="1">
         <v>46235</v>
       </c>
@@ -14317,8 +14380,17 @@
       <c r="G433" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H433">
+        <v>84</v>
+      </c>
+      <c r="I433">
+        <v>83</v>
+      </c>
+      <c r="J433">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A434" s="1">
         <v>46235</v>
       </c>
@@ -14340,8 +14412,17 @@
       <c r="G434" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H434">
+        <v>94</v>
+      </c>
+      <c r="I434">
+        <v>92</v>
+      </c>
+      <c r="J434">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A435" s="1">
         <v>46235</v>
       </c>
@@ -14363,8 +14444,17 @@
       <c r="G435" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H435">
+        <v>92</v>
+      </c>
+      <c r="I435">
+        <v>94</v>
+      </c>
+      <c r="J435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A436" s="1">
         <v>46236</v>
       </c>
@@ -14386,8 +14476,17 @@
       <c r="G436" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H436">
+        <v>63</v>
+      </c>
+      <c r="I436">
+        <v>83</v>
+      </c>
+      <c r="J436">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A437" s="1">
         <v>46236</v>
       </c>
@@ -14409,8 +14508,17 @@
       <c r="G437" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H437">
+        <v>83</v>
+      </c>
+      <c r="I437">
+        <v>63</v>
+      </c>
+      <c r="J437">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A438" s="1">
         <v>46236</v>
       </c>
@@ -14432,8 +14540,17 @@
       <c r="G438" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H438">
+        <v>79</v>
+      </c>
+      <c r="I438">
+        <v>96</v>
+      </c>
+      <c r="J438">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A439" s="1">
         <v>46236</v>
       </c>
@@ -14455,8 +14572,17 @@
       <c r="G439" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H439">
+        <v>96</v>
+      </c>
+      <c r="I439">
+        <v>79</v>
+      </c>
+      <c r="J439">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A440" s="1">
         <v>46236</v>
       </c>
@@ -14478,8 +14604,17 @@
       <c r="G440" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H440">
+        <v>100</v>
+      </c>
+      <c r="I440">
+        <v>108</v>
+      </c>
+      <c r="J440">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A441" s="1">
         <v>46236</v>
       </c>
@@ -14501,8 +14636,17 @@
       <c r="G441" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H441">
+        <v>108</v>
+      </c>
+      <c r="I441">
+        <v>100</v>
+      </c>
+      <c r="J441">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A442" s="1">
         <v>46236</v>
       </c>
@@ -14524,8 +14668,17 @@
       <c r="G442" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H442">
+        <v>106</v>
+      </c>
+      <c r="I442">
+        <v>101</v>
+      </c>
+      <c r="J442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A443" s="1">
         <v>46236</v>
       </c>
@@ -14547,8 +14700,17 @@
       <c r="G443" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H443">
+        <v>101</v>
+      </c>
+      <c r="I443">
+        <v>106</v>
+      </c>
+      <c r="J443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A444" s="1">
         <v>46237</v>
       </c>
@@ -14570,8 +14732,17 @@
       <c r="G444" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H444">
+        <v>109</v>
+      </c>
+      <c r="I444">
+        <v>87</v>
+      </c>
+      <c r="J444">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A445" s="1">
         <v>46237</v>
       </c>
@@ -14593,8 +14764,17 @@
       <c r="G445" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H445">
+        <v>87</v>
+      </c>
+      <c r="I445">
+        <v>109</v>
+      </c>
+      <c r="J445">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A446" s="1">
         <v>46237</v>
       </c>
@@ -14616,8 +14796,17 @@
       <c r="G446" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H446">
+        <v>106</v>
+      </c>
+      <c r="I446">
+        <v>101</v>
+      </c>
+      <c r="J446">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A447" s="1">
         <v>46237</v>
       </c>
@@ -14639,8 +14828,17 @@
       <c r="G447" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H447">
+        <v>101</v>
+      </c>
+      <c r="I447">
+        <v>106</v>
+      </c>
+      <c r="J447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A448" s="1">
         <v>46237</v>
       </c>
@@ -14662,8 +14860,17 @@
       <c r="G448" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H448">
+        <v>83</v>
+      </c>
+      <c r="I448">
+        <v>95</v>
+      </c>
+      <c r="J448">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A449" s="1">
         <v>46237</v>
       </c>
@@ -14685,8 +14892,17 @@
       <c r="G449" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H449">
+        <v>95</v>
+      </c>
+      <c r="I449">
+        <v>83</v>
+      </c>
+      <c r="J449">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A450" s="1">
         <v>46238</v>
       </c>
@@ -14709,7 +14925,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A451" s="1">
         <v>46238</v>
       </c>
@@ -14732,7 +14948,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A452" s="1">
         <v>46239</v>
       </c>
@@ -14755,7 +14971,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A453" s="1">
         <v>46239</v>
       </c>
@@ -14778,7 +14994,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A454" s="1">
         <v>46239</v>
       </c>
@@ -14801,7 +15017,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A455" s="1">
         <v>46239</v>
       </c>
@@ -14824,7 +15040,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A456" s="1">
         <v>46239</v>
       </c>
@@ -14847,7 +15063,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A457" s="1">
         <v>46239</v>
       </c>
@@ -14870,7 +15086,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A458" s="1">
         <v>46239</v>
       </c>
@@ -14893,7 +15109,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A459" s="1">
         <v>46239</v>
       </c>
@@ -14916,7 +15132,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A460" s="1">
         <v>46240</v>
       </c>
@@ -14939,7 +15155,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A461" s="1">
         <v>46240</v>
       </c>
@@ -14962,7 +15178,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A462" s="1">
         <v>46240</v>
       </c>
@@ -14985,7 +15201,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A463" s="1">
         <v>46240</v>
       </c>
@@ -15008,7 +15224,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A464" s="1">
         <v>46240</v>
       </c>

--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1742D1D-7C1B-441B-B2D9-3B04FDF512BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAFC8EED-634A-4ACC-8333-1AE31EE9D54C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -14924,6 +14924,15 @@
       <c r="G450" t="s">
         <v>24</v>
       </c>
+      <c r="H450">
+        <v>81</v>
+      </c>
+      <c r="I450">
+        <v>92</v>
+      </c>
+      <c r="J450">
+        <v>0</v>
+      </c>
     </row>
     <row r="451" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A451" s="1">
@@ -14946,6 +14955,15 @@
       </c>
       <c r="G451" t="s">
         <v>25</v>
+      </c>
+      <c r="H451">
+        <v>92</v>
+      </c>
+      <c r="I451">
+        <v>81</v>
+      </c>
+      <c r="J451">
+        <v>0</v>
       </c>
     </row>
     <row r="452" spans="1:10" x14ac:dyDescent="0.35">

--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAFC8EED-634A-4ACC-8333-1AE31EE9D54C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85AFB8B5-28D5-4C5A-AA02-A13E2223546D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -14988,6 +14988,15 @@
       <c r="G452" t="s">
         <v>24</v>
       </c>
+      <c r="H452">
+        <v>82</v>
+      </c>
+      <c r="I452">
+        <v>96</v>
+      </c>
+      <c r="J452">
+        <v>0</v>
+      </c>
     </row>
     <row r="453" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A453" s="1">
@@ -15011,6 +15020,15 @@
       <c r="G453" t="s">
         <v>25</v>
       </c>
+      <c r="H453">
+        <v>96</v>
+      </c>
+      <c r="I453">
+        <v>82</v>
+      </c>
+      <c r="J453">
+        <v>0</v>
+      </c>
     </row>
     <row r="454" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A454" s="1">
@@ -15034,6 +15052,15 @@
       <c r="G454" t="s">
         <v>24</v>
       </c>
+      <c r="H454">
+        <v>88</v>
+      </c>
+      <c r="I454">
+        <v>95</v>
+      </c>
+      <c r="J454">
+        <v>0</v>
+      </c>
     </row>
     <row r="455" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A455" s="1">
@@ -15057,6 +15084,15 @@
       <c r="G455" t="s">
         <v>25</v>
       </c>
+      <c r="H455">
+        <v>95</v>
+      </c>
+      <c r="I455">
+        <v>88</v>
+      </c>
+      <c r="J455">
+        <v>0</v>
+      </c>
     </row>
     <row r="456" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A456" s="1">
@@ -15080,6 +15116,15 @@
       <c r="G456" t="s">
         <v>24</v>
       </c>
+      <c r="H456">
+        <v>86</v>
+      </c>
+      <c r="I456">
+        <v>92</v>
+      </c>
+      <c r="J456">
+        <v>0</v>
+      </c>
     </row>
     <row r="457" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A457" s="1">
@@ -15103,6 +15148,15 @@
       <c r="G457" t="s">
         <v>25</v>
       </c>
+      <c r="H457">
+        <v>92</v>
+      </c>
+      <c r="I457">
+        <v>86</v>
+      </c>
+      <c r="J457">
+        <v>0</v>
+      </c>
     </row>
     <row r="458" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A458" s="1">
@@ -15126,6 +15180,15 @@
       <c r="G458" t="s">
         <v>24</v>
       </c>
+      <c r="H458">
+        <v>92</v>
+      </c>
+      <c r="I458">
+        <v>96</v>
+      </c>
+      <c r="J458">
+        <v>0</v>
+      </c>
     </row>
     <row r="459" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A459" s="1">
@@ -15148,6 +15211,15 @@
       </c>
       <c r="G459" t="s">
         <v>25</v>
+      </c>
+      <c r="H459">
+        <v>96</v>
+      </c>
+      <c r="I459">
+        <v>92</v>
+      </c>
+      <c r="J459">
+        <v>0</v>
       </c>
     </row>
     <row r="460" spans="1:10" x14ac:dyDescent="0.35">

--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85AFB8B5-28D5-4C5A-AA02-A13E2223546D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0A87D1-EAE1-4ECA-A36A-98762976EB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -15244,6 +15244,15 @@
       <c r="G460" t="s">
         <v>24</v>
       </c>
+      <c r="H460">
+        <v>86</v>
+      </c>
+      <c r="I460">
+        <v>84</v>
+      </c>
+      <c r="J460">
+        <v>1</v>
+      </c>
     </row>
     <row r="461" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A461" s="1">
@@ -15267,6 +15276,15 @@
       <c r="G461" t="s">
         <v>25</v>
       </c>
+      <c r="H461">
+        <v>84</v>
+      </c>
+      <c r="I461">
+        <v>86</v>
+      </c>
+      <c r="J461">
+        <v>1</v>
+      </c>
     </row>
     <row r="462" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A462" s="1">
@@ -15290,6 +15308,15 @@
       <c r="G462" t="s">
         <v>24</v>
       </c>
+      <c r="H462">
+        <v>89</v>
+      </c>
+      <c r="I462">
+        <v>82</v>
+      </c>
+      <c r="J462">
+        <v>0</v>
+      </c>
     </row>
     <row r="463" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A463" s="1">
@@ -15313,6 +15340,15 @@
       <c r="G463" t="s">
         <v>25</v>
       </c>
+      <c r="H463">
+        <v>82</v>
+      </c>
+      <c r="I463">
+        <v>89</v>
+      </c>
+      <c r="J463">
+        <v>0</v>
+      </c>
     </row>
     <row r="464" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A464" s="1">
@@ -15336,8 +15372,17 @@
       <c r="G464" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H464">
+        <v>83</v>
+      </c>
+      <c r="I464">
+        <v>97</v>
+      </c>
+      <c r="J464">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A465" s="1">
         <v>46240</v>
       </c>
@@ -15359,8 +15404,17 @@
       <c r="G465" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H465">
+        <v>97</v>
+      </c>
+      <c r="I465">
+        <v>83</v>
+      </c>
+      <c r="J465">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A466" s="1">
         <v>46241</v>
       </c>
@@ -15383,7 +15437,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A467" s="1">
         <v>46241</v>
       </c>
@@ -15406,7 +15460,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A468" s="1">
         <v>46241</v>
       </c>
@@ -15429,7 +15483,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A469" s="1">
         <v>46241</v>
       </c>
@@ -15452,7 +15506,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A470" s="1">
         <v>46241</v>
       </c>
@@ -15475,7 +15529,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A471" s="1">
         <v>46241</v>
       </c>
@@ -15498,7 +15552,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A472" s="1">
         <v>46242</v>
       </c>
@@ -15521,7 +15575,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A473" s="1">
         <v>46242</v>
       </c>
@@ -15544,7 +15598,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A474" s="1">
         <v>46242</v>
       </c>
@@ -15567,7 +15621,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A475" s="1">
         <v>46242</v>
       </c>
@@ -15590,7 +15644,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A476" s="1">
         <v>46242</v>
       </c>
@@ -15613,7 +15667,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A477" s="1">
         <v>46242</v>
       </c>
@@ -15636,7 +15690,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A478" s="1">
         <v>46243</v>
       </c>
@@ -15659,7 +15713,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A479" s="1">
         <v>46243</v>
       </c>
@@ -15682,7 +15736,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A480" s="1">
         <v>46243</v>
       </c>

--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0A87D1-EAE1-4ECA-A36A-98762976EB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3915ABB6-F4CA-4E61-A212-7B1C95C467CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -15436,6 +15436,15 @@
       <c r="G466" t="s">
         <v>24</v>
       </c>
+      <c r="H466">
+        <v>72</v>
+      </c>
+      <c r="I466">
+        <v>75</v>
+      </c>
+      <c r="J466">
+        <v>0</v>
+      </c>
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A467" s="1">
@@ -15459,6 +15468,15 @@
       <c r="G467" t="s">
         <v>25</v>
       </c>
+      <c r="H467">
+        <v>75</v>
+      </c>
+      <c r="I467">
+        <v>72</v>
+      </c>
+      <c r="J467">
+        <v>0</v>
+      </c>
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A468" s="1">
@@ -15482,6 +15500,15 @@
       <c r="G468" t="s">
         <v>24</v>
       </c>
+      <c r="H468">
+        <v>94</v>
+      </c>
+      <c r="I468">
+        <v>76</v>
+      </c>
+      <c r="J468">
+        <v>0</v>
+      </c>
     </row>
     <row r="469" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A469" s="1">
@@ -15505,6 +15532,15 @@
       <c r="G469" t="s">
         <v>25</v>
       </c>
+      <c r="H469">
+        <v>76</v>
+      </c>
+      <c r="I469">
+        <v>94</v>
+      </c>
+      <c r="J469">
+        <v>0</v>
+      </c>
     </row>
     <row r="470" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A470" s="1">
@@ -15528,6 +15564,15 @@
       <c r="G470" t="s">
         <v>24</v>
       </c>
+      <c r="H470">
+        <v>74</v>
+      </c>
+      <c r="I470">
+        <v>79</v>
+      </c>
+      <c r="J470">
+        <v>0</v>
+      </c>
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A471" s="1">
@@ -15550,6 +15595,15 @@
       </c>
       <c r="G471" t="s">
         <v>25</v>
+      </c>
+      <c r="H471">
+        <v>79</v>
+      </c>
+      <c r="I471">
+        <v>74</v>
+      </c>
+      <c r="J471">
+        <v>0</v>
       </c>
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.35">

--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3915ABB6-F4CA-4E61-A212-7B1C95C467CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FFAB44C-E997-4904-AFFC-0E9942D5C964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -15628,6 +15628,15 @@
       <c r="G472" t="s">
         <v>24</v>
       </c>
+      <c r="H472">
+        <v>90</v>
+      </c>
+      <c r="I472">
+        <v>86</v>
+      </c>
+      <c r="J472">
+        <v>0</v>
+      </c>
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A473" s="1">
@@ -15651,6 +15660,15 @@
       <c r="G473" t="s">
         <v>25</v>
       </c>
+      <c r="H473">
+        <v>86</v>
+      </c>
+      <c r="I473">
+        <v>90</v>
+      </c>
+      <c r="J473">
+        <v>0</v>
+      </c>
     </row>
     <row r="474" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A474" s="1">
@@ -15674,6 +15692,15 @@
       <c r="G474" t="s">
         <v>24</v>
       </c>
+      <c r="H474">
+        <v>87</v>
+      </c>
+      <c r="I474">
+        <v>98</v>
+      </c>
+      <c r="J474">
+        <v>0</v>
+      </c>
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A475" s="1">
@@ -15697,6 +15724,15 @@
       <c r="G475" t="s">
         <v>25</v>
       </c>
+      <c r="H475">
+        <v>98</v>
+      </c>
+      <c r="I475">
+        <v>87</v>
+      </c>
+      <c r="J475">
+        <v>0</v>
+      </c>
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A476" s="1">
@@ -15720,6 +15756,15 @@
       <c r="G476" t="s">
         <v>24</v>
       </c>
+      <c r="H476">
+        <v>93</v>
+      </c>
+      <c r="I476">
+        <v>100</v>
+      </c>
+      <c r="J476">
+        <v>0</v>
+      </c>
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A477" s="1">
@@ -15742,6 +15787,15 @@
       </c>
       <c r="G477" t="s">
         <v>25</v>
+      </c>
+      <c r="H477">
+        <v>100</v>
+      </c>
+      <c r="I477">
+        <v>93</v>
+      </c>
+      <c r="J477">
+        <v>0</v>
       </c>
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.35">

--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FFAB44C-E997-4904-AFFC-0E9942D5C964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE4A146-5277-44DB-86C9-D1B1B7896361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -15820,6 +15820,15 @@
       <c r="G478" t="s">
         <v>24</v>
       </c>
+      <c r="H478">
+        <v>84</v>
+      </c>
+      <c r="I478">
+        <v>78</v>
+      </c>
+      <c r="J478">
+        <v>0</v>
+      </c>
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A479" s="1">
@@ -15843,6 +15852,15 @@
       <c r="G479" t="s">
         <v>25</v>
       </c>
+      <c r="H479">
+        <v>78</v>
+      </c>
+      <c r="I479">
+        <v>84</v>
+      </c>
+      <c r="J479">
+        <v>0</v>
+      </c>
     </row>
     <row r="480" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A480" s="1">
@@ -15866,8 +15884,17 @@
       <c r="G480" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H480">
+        <v>90</v>
+      </c>
+      <c r="I480">
+        <v>103</v>
+      </c>
+      <c r="J480">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A481" s="1">
         <v>46243</v>
       </c>
@@ -15889,8 +15916,17 @@
       <c r="G481" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H481">
+        <v>103</v>
+      </c>
+      <c r="I481">
+        <v>90</v>
+      </c>
+      <c r="J481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A482" s="1">
         <v>46243</v>
       </c>
@@ -15912,8 +15948,17 @@
       <c r="G482" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H482">
+        <v>71</v>
+      </c>
+      <c r="I482">
+        <v>111</v>
+      </c>
+      <c r="J482">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A483" s="1">
         <v>46243</v>
       </c>
@@ -15935,8 +15980,17 @@
       <c r="G483" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H483">
+        <v>111</v>
+      </c>
+      <c r="I483">
+        <v>71</v>
+      </c>
+      <c r="J483">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A484" s="1">
         <v>46243</v>
       </c>
@@ -15958,8 +16012,17 @@
       <c r="G484" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H484">
+        <v>75</v>
+      </c>
+      <c r="I484">
+        <v>95</v>
+      </c>
+      <c r="J484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A485" s="1">
         <v>46243</v>
       </c>
@@ -15981,8 +16044,17 @@
       <c r="G485" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H485">
+        <v>95</v>
+      </c>
+      <c r="I485">
+        <v>75</v>
+      </c>
+      <c r="J485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A486" s="1">
         <v>46244</v>
       </c>
@@ -16005,7 +16077,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A487" s="1">
         <v>46244</v>
       </c>
@@ -16028,7 +16100,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A488" s="1">
         <v>46244</v>
       </c>
@@ -16051,7 +16123,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A489" s="1">
         <v>46244</v>
       </c>
@@ -16074,7 +16146,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A490" s="1">
         <v>46245</v>
       </c>
@@ -16097,7 +16169,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A491" s="1">
         <v>46245</v>
       </c>
@@ -16120,7 +16192,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A492" s="1">
         <v>46245</v>
       </c>
@@ -16143,7 +16215,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A493" s="1">
         <v>46245</v>
       </c>
@@ -16166,7 +16238,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A494" s="1">
         <v>46245</v>
       </c>
@@ -16189,7 +16261,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A495" s="1">
         <v>46245</v>
       </c>
@@ -16212,7 +16284,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A496" s="1">
         <v>46246</v>
       </c>

--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE4A146-5277-44DB-86C9-D1B1B7896361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B43551D-0394-4FFE-B375-54EAB25A0435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -16076,6 +16076,15 @@
       <c r="G486" t="s">
         <v>24</v>
       </c>
+      <c r="H486">
+        <v>95</v>
+      </c>
+      <c r="I486">
+        <v>107</v>
+      </c>
+      <c r="J486">
+        <v>0</v>
+      </c>
     </row>
     <row r="487" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A487" s="1">
@@ -16099,6 +16108,15 @@
       <c r="G487" t="s">
         <v>25</v>
       </c>
+      <c r="H487">
+        <v>107</v>
+      </c>
+      <c r="I487">
+        <v>95</v>
+      </c>
+      <c r="J487">
+        <v>0</v>
+      </c>
     </row>
     <row r="488" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A488" s="1">
@@ -16122,6 +16140,15 @@
       <c r="G488" t="s">
         <v>24</v>
       </c>
+      <c r="H488">
+        <v>88</v>
+      </c>
+      <c r="I488">
+        <v>97</v>
+      </c>
+      <c r="J488">
+        <v>0</v>
+      </c>
     </row>
     <row r="489" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A489" s="1">
@@ -16144,6 +16171,15 @@
       </c>
       <c r="G489" t="s">
         <v>25</v>
+      </c>
+      <c r="H489">
+        <v>97</v>
+      </c>
+      <c r="I489">
+        <v>88</v>
+      </c>
+      <c r="J489">
+        <v>0</v>
       </c>
     </row>
     <row r="490" spans="1:10" x14ac:dyDescent="0.35">

--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B43551D-0394-4FFE-B375-54EAB25A0435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{795ED4F0-E0E0-4503-8422-AB0DB130041D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -16204,6 +16204,15 @@
       <c r="G490" t="s">
         <v>24</v>
       </c>
+      <c r="H490">
+        <v>92</v>
+      </c>
+      <c r="I490">
+        <v>106</v>
+      </c>
+      <c r="J490">
+        <v>0</v>
+      </c>
     </row>
     <row r="491" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A491" s="1">
@@ -16227,6 +16236,15 @@
       <c r="G491" t="s">
         <v>25</v>
       </c>
+      <c r="H491">
+        <v>106</v>
+      </c>
+      <c r="I491">
+        <v>92</v>
+      </c>
+      <c r="J491">
+        <v>0</v>
+      </c>
     </row>
     <row r="492" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A492" s="1">
@@ -16250,6 +16268,15 @@
       <c r="G492" t="s">
         <v>24</v>
       </c>
+      <c r="H492">
+        <v>94</v>
+      </c>
+      <c r="I492">
+        <v>87</v>
+      </c>
+      <c r="J492">
+        <v>0</v>
+      </c>
     </row>
     <row r="493" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A493" s="1">
@@ -16273,6 +16300,15 @@
       <c r="G493" t="s">
         <v>25</v>
       </c>
+      <c r="H493">
+        <v>87</v>
+      </c>
+      <c r="I493">
+        <v>94</v>
+      </c>
+      <c r="J493">
+        <v>0</v>
+      </c>
     </row>
     <row r="494" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A494" s="1">
@@ -16296,6 +16332,15 @@
       <c r="G494" t="s">
         <v>24</v>
       </c>
+      <c r="H494">
+        <v>76</v>
+      </c>
+      <c r="I494">
+        <v>86</v>
+      </c>
+      <c r="J494">
+        <v>0</v>
+      </c>
     </row>
     <row r="495" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A495" s="1">
@@ -16318,6 +16363,15 @@
       </c>
       <c r="G495" t="s">
         <v>25</v>
+      </c>
+      <c r="H495">
+        <v>86</v>
+      </c>
+      <c r="I495">
+        <v>76</v>
+      </c>
+      <c r="J495">
+        <v>0</v>
       </c>
     </row>
     <row r="496" spans="1:10" x14ac:dyDescent="0.35">
